--- a/data/export/2026-10-03-浦东78路.xlsx
+++ b/data/export/2026-10-03-浦东78路.xlsx
@@ -427,12 +427,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC4"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:37</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,33 +693,37 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>1/9</t>
         </is>
       </c>
     </row>
@@ -723,22 +731,22 @@
       <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>06:45</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -771,12 +779,12 @@
       <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -790,7 +798,7 @@
       <c r="T3" s="2" t="inlineStr"/>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="V3" s="2" t="inlineStr">
@@ -815,7 +823,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -826,7 +834,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/9</t>
         </is>
       </c>
     </row>
@@ -834,7 +842,7 @@
       <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -844,7 +852,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -887,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -901,7 +909,7 @@
       <c r="T4" s="2" t="inlineStr"/>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -937,7 +945,907 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr"/>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>89分钟</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="inlineStr"/>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>2/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>1/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-03-浦东78路.xlsx
+++ b/data/export/2026-10-03-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC12"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -642,24 +642,24 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>07:37</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/9</t>
+          <t>1/12</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -834,7 +834,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -862,32 +862,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -895,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -919,33 +923,37 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/12</t>
         </is>
       </c>
     </row>
@@ -983,24 +991,24 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1010,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1049,22 +1057,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/9</t>
+          <t>2/12</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1164,7 +1172,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1175,7 +1183,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1203,32 +1211,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -1236,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1260,33 +1272,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>4/12</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1397,7 +1413,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1474,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1507,12 +1523,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>1/9</t>
+          <t>1/12</t>
         </is>
       </c>
     </row>
@@ -1573,7 +1589,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1623,7 +1639,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1700,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1734,7 +1750,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1742,22 +1758,22 @@
       <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1790,12 +1806,12 @@
       <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1839,13 +1855,802 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>2/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB12" s="2" t="inlineStr"/>
-      <c r="AC12" s="2" t="inlineStr">
-        <is>
-          <t>—/9</t>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>2/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>4/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-03-浦东78路.xlsx
+++ b/data/export/2026-10-03-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:AC23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -834,7 +834,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1100,32 +1100,36 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -1133,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1157,17 +1161,17 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1177,13 +1181,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1241,12 @@
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1248,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1302,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1330,32 +1338,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -1363,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1387,33 +1399,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1441,32 +1457,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -1474,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1498,37 +1518,37 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1556,32 +1576,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -1589,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1613,17 +1637,17 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
@@ -1633,13 +1657,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1667,32 +1695,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -1700,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1724,17 +1756,17 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
@@ -1744,13 +1776,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1865,7 +1901,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1976,7 +2012,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2073,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2087,7 +2123,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2184,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2202,7 +2238,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2299,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2307,13 +2343,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2374,7 +2414,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2424,7 +2464,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2525,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2539,7 +2579,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2600,7 +2640,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2650,7 +2690,459 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-03-浦东78路.xlsx
+++ b/data/export/2026-10-03-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC23"/>
+  <dimension ref="A1:AC27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3146,6 +3146,462 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-03-浦东78路.xlsx
+++ b/data/export/2026-10-03-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC27"/>
+  <dimension ref="A1:AC35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,22 +1295,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2040,32 +2040,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -2073,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2097,33 +2101,37 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2192,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2223,7 +2231,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2238,7 +2246,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2266,32 +2274,36 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -2299,7 +2311,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2323,17 +2335,17 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
@@ -2343,17 +2355,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2381,32 +2393,36 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
@@ -2414,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2438,33 +2454,37 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2492,32 +2512,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -2525,7 +2549,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2549,37 +2573,37 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2607,32 +2631,36 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -2640,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2664,33 +2692,37 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2718,32 +2750,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -2751,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2775,33 +2811,37 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2829,32 +2869,36 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -2862,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2886,33 +2930,37 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2973,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3027,7 +3075,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3136,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3127,7 +3175,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3142,7 +3190,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3203,7 +3251,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3257,7 +3305,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3318,7 +3366,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3429,7 +3477,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3483,7 +3531,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3491,22 +3539,22 @@
       <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3539,12 +3587,12 @@
       <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3558,47 +3606,967 @@
       <c r="T27" s="2" t="inlineStr"/>
       <c r="U27" s="2" t="inlineStr">
         <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W27" s="2" t="inlineStr">
+      <c r="W28" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X27" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y27" s="2" t="inlineStr">
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z27" s="2" t="inlineStr">
+      <c r="Z28" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
+      <c r="AA28" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB27" s="2" t="inlineStr">
+      <c r="AB28" s="2" t="inlineStr">
         <is>
           <t>82.0</t>
         </is>
       </c>
-      <c r="AC27" s="2" t="inlineStr">
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
         <is>
           <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-03-浦东78路.xlsx
+++ b/data/export/2026-10-03-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC35"/>
+  <dimension ref="A1:AC41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,18 +823,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -899,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,22 +942,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1062,17 +1066,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1191,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1310,7 +1314,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,22 +1418,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1538,17 +1542,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1657,17 +1661,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,22 +1775,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1886,22 +1890,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2001,18 +2005,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2077,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2121,17 +2129,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2236,17 +2244,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2365,7 +2373,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2430,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2469,22 +2477,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2603,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2707,7 +2715,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2787,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2841,7 +2849,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2960,7 +2968,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2988,32 +2996,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -3021,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3045,37 +3057,37 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3103,32 +3115,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -3136,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3160,17 +3176,17 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3180,17 +3196,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3218,32 +3234,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -3251,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3275,17 +3295,17 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3295,17 +3315,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3333,32 +3353,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -3366,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3390,33 +3414,37 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3444,32 +3472,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -3477,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3501,37 +3533,37 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3559,32 +3591,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -3592,7 +3628,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3616,17 +3652,17 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
@@ -3636,17 +3672,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3674,32 +3710,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -3707,7 +3747,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3731,37 +3771,37 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3789,32 +3829,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
@@ -3822,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3846,37 +3890,37 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3904,32 +3948,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -3937,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3961,17 +4009,17 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -3981,17 +4029,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4052,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4106,7 +4154,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4215,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4206,7 +4254,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4282,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4336,7 +4384,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4397,7 +4445,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4451,7 +4499,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4512,7 +4560,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4556,17 +4604,707 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>79.3</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB35" s="2" t="inlineStr">
-        <is>
-          <t>78.0</t>
-        </is>
-      </c>
-      <c r="AC35" s="2" t="inlineStr">
-        <is>
-          <t>6/14</t>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>81.5</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-03-浦东78路.xlsx
+++ b/data/export/2026-10-03-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC41"/>
+  <dimension ref="A1:AC47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,14 +1180,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
           <t>77.5</t>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1304,17 +1304,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,22 +1418,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1542,17 +1542,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2358,14 +2358,14 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
           <t>77.5</t>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2601,17 +2601,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2720,17 +2720,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2834,22 +2834,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2953,22 +2953,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3072,22 +3072,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3196,17 +3196,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3429,7 +3429,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3682,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3747,7 +3747,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -3839,24 +3839,24 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -4067,32 +4067,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -4100,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4124,17 +4128,17 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4144,17 +4148,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -4182,32 +4186,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -4215,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4239,17 +4247,17 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
@@ -4259,17 +4267,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -4297,32 +4305,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -4330,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4354,37 +4366,37 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -4412,32 +4424,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -4445,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4469,37 +4485,37 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -4527,32 +4543,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -4560,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4584,17 +4604,17 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -4604,17 +4624,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4642,32 +4662,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -4675,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4699,37 +4723,37 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -4790,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4844,7 +4868,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4905,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4959,7 +4983,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5059,7 +5083,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5074,7 +5098,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5179,17 +5203,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5274,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5299,12 +5323,698 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>85.3</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>14/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr"/>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>77.5</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-03-浦东78路.xlsx
+++ b/data/export/2026-10-03-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC47"/>
+  <dimension ref="A1:AC52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -828,17 +828,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -947,17 +947,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1895,17 +1895,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2010,17 +2010,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2477,17 +2477,17 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2953,17 +2953,17 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3082,7 +3082,7 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3434,17 +3434,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3791,17 +3791,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3905,17 +3905,17 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4267,12 +4267,12 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4381,17 +4381,17 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4505,12 +4505,12 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4672,12 +4672,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -4896,32 +4896,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -4929,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4953,17 +4957,17 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -4973,17 +4977,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -5011,32 +5015,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -5044,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5068,17 +5076,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5088,17 +5096,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -5126,32 +5134,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -5159,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5183,17 +5195,17 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -5203,12 +5215,12 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5241,32 +5253,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
@@ -5274,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5298,32 +5314,32 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5356,32 +5372,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -5389,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5413,17 +5433,17 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
@@ -5433,12 +5453,12 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5471,32 +5491,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -5504,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5528,32 +5552,32 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5619,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5668,7 +5692,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5734,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5773,7 +5797,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5845,7 +5869,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5889,17 +5913,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5984,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6018,6 +6042,577 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>79.7</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>76.3</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr"/>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-03-浦东78路.xlsx
+++ b/data/export/2026-10-03-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC52"/>
+  <dimension ref="A1:AC57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,22 +823,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,22 +1180,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,22 +1418,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2005,22 +2005,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2358,22 +2358,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2482,17 +2482,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2963,12 +2963,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3072,22 +3072,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3429,22 +3429,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3910,17 +3910,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4391,12 +4391,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4738,22 +4738,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -4987,7 +4987,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5091,22 +5091,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5334,17 +5334,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -5382,24 +5382,24 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5458,7 +5458,7 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5501,12 +5501,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -5610,32 +5610,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -5643,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5667,37 +5671,37 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -5725,32 +5729,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>11:50</t>
@@ -5758,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5782,17 +5790,17 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5802,13 +5810,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB45" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5836,32 +5848,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -5869,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5893,37 +5909,37 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -5951,32 +5967,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -5984,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6008,37 +6028,37 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -6066,32 +6086,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
@@ -6099,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6123,17 +6147,17 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -6143,17 +6167,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -6214,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6253,7 +6277,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6329,7 +6353,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6378,12 +6402,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -6444,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6559,7 +6583,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6603,13 +6627,592 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB52" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>15/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>76.7</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>79.3</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-03-浦东78路.xlsx
+++ b/data/export/2026-10-03-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC57"/>
+  <dimension ref="A1:AC63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1066,17 +1066,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1190,12 +1190,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1656,14 +1656,14 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
           <t>79.0</t>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,22 +1775,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2015,12 +2015,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2244,17 +2244,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2368,12 +2368,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2477,22 +2477,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2953,17 +2953,17 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3310,14 +3310,14 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
           <t>79.0</t>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3439,12 +3439,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3548,22 +3548,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3672,17 +3672,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4381,17 +4381,17 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4853,22 +4853,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5101,12 +5101,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5329,22 +5329,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5567,17 +5567,17 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -5858,24 +5858,24 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -5977,24 +5977,24 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -6096,24 +6096,24 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6162,22 +6162,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -6205,32 +6205,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6238,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6262,17 +6266,17 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
@@ -6282,17 +6286,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -6320,32 +6324,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -6353,7 +6361,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6377,32 +6385,32 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6435,32 +6443,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -6468,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6492,29 +6504,29 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
           <t>79.0</t>
@@ -6522,7 +6534,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -6583,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6637,7 +6649,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -6665,32 +6677,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -6698,7 +6714,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6722,37 +6738,37 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6829,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6928,7 +6944,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6977,12 +6993,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -7043,7 +7059,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7092,12 +7108,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -7105,22 +7121,22 @@
       <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -7153,12 +7169,12 @@
       <c r="M57" s="2" t="inlineStr"/>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7172,47 +7188,737 @@
       <c r="T57" s="2" t="inlineStr"/>
       <c r="U57" s="2" t="inlineStr">
         <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
           <t>15:20</t>
         </is>
       </c>
-      <c r="V57" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W57" s="2" t="inlineStr">
+      <c r="W58" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X57" s="2" t="inlineStr">
+      <c r="X58" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y57" s="2" t="inlineStr">
+      <c r="Y58" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z57" s="2" t="inlineStr">
+      <c r="Z58" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA57" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB57" s="2" t="inlineStr">
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>77.3</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>80.2</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
         <is>
           <t>79.0</t>
         </is>
       </c>
-      <c r="AC57" s="2" t="inlineStr">
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>14/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
         <is>
           <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>77.2</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-03-浦东78路.xlsx
+++ b/data/export/2026-10-03-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC63"/>
+  <dimension ref="A1:AC71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,14 +708,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>78.2</t>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,17 +823,17 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1066,12 +1066,12 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,22 +1418,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1537,14 +1537,14 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
           <t>78.2</t>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1661,17 +1661,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1785,12 +1785,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2005,17 +2005,17 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2363,17 +2363,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2715,17 +2715,17 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2834,14 +2834,14 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
           <t>75.0</t>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3072,22 +3072,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3191,14 +3191,14 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>78.2</t>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3315,17 +3315,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3429,17 +3429,17 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3558,12 +3558,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4262,17 +4262,17 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4500,14 +4500,14 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
           <t>75.0</t>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4619,14 +4619,14 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
           <t>78.2</t>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4738,22 +4738,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4863,12 +4863,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5091,17 +5091,17 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5210,17 +5210,17 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5448,14 +5448,14 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
           <t>75.0</t>
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5686,22 +5686,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5805,22 +5805,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -5885,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5924,17 +5924,17 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6048,17 +6048,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -6123,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6286,12 +6286,12 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6524,17 +6524,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -6562,32 +6562,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>11:50</t>
@@ -6595,7 +6599,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6619,37 +6623,37 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -6687,24 +6691,24 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6714,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6763,12 +6767,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -6796,32 +6800,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6829,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6853,37 +6861,37 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -6911,32 +6919,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -6944,7 +6956,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6968,17 +6980,17 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
@@ -6988,17 +7000,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -7026,32 +7038,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -7059,7 +7075,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7083,32 +7099,32 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7141,32 +7157,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -7174,7 +7194,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7198,32 +7218,32 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA57" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7256,32 +7276,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -7289,7 +7313,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7313,17 +7337,17 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7333,12 +7357,12 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7404,7 +7428,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7443,7 +7467,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7486,32 +7510,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -7519,7 +7547,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7543,17 +7571,17 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
@@ -7563,17 +7591,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -7634,7 +7662,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7688,7 +7716,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -7749,7 +7777,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7798,12 +7826,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -7864,7 +7892,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7918,7 +7946,927 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>80.8</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>14/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>79.7</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>79.5</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>78.2</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>74.5</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>80.2</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-03-浦东78路.xlsx
+++ b/data/export/2026-10-03-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC71"/>
+  <dimension ref="A1:AC78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1299,22 +1299,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1656,22 +1656,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,22 +1775,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2482,17 +2482,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2596,22 +2596,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2834,17 +2834,17 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2953,22 +2953,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3310,22 +3310,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3548,22 +3548,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3910,17 +3910,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4039,7 +4039,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4143,22 +4143,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4381,22 +4381,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4500,17 +4500,17 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4853,22 +4853,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5334,17 +5334,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5448,17 +5448,17 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5567,22 +5567,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5885,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6167,17 +6167,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6400,22 +6400,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6519,22 +6519,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -6599,7 +6599,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -6718,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6757,22 +6757,22 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6995,7 +6995,7 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -7194,7 +7194,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7298,12 +7298,12 @@
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -7313,7 +7313,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7352,7 +7352,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7395,32 +7395,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
@@ -7428,7 +7432,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7452,17 +7456,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7472,17 +7476,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -7520,24 +7524,24 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7547,7 +7551,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7586,22 +7590,22 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -7629,32 +7633,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -7662,7 +7670,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7686,37 +7694,37 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -7744,32 +7752,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -7777,7 +7789,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7801,37 +7813,37 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -7859,32 +7871,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -7892,7 +7908,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7916,37 +7932,37 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA63" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -7974,32 +7990,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -8007,7 +8027,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8031,32 +8051,32 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA64" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8122,7 +8142,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8176,7 +8196,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8257,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8291,7 +8311,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -8352,7 +8372,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8406,7 +8426,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -8467,7 +8487,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8521,7 +8541,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -8582,7 +8602,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8636,7 +8656,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -8697,7 +8717,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8759,22 +8779,22 @@
       <c r="A71" s="2" t="inlineStr"/>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>17:10</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -8807,12 +8827,12 @@
       <c r="M71" s="2" t="inlineStr"/>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8826,47 +8846,852 @@
       <c r="T71" s="2" t="inlineStr"/>
       <c r="U71" s="2" t="inlineStr">
         <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>74.5</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
           <t>17:10</t>
         </is>
       </c>
-      <c r="V71" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W71" s="2" t="inlineStr">
+      <c r="W72" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X71" s="2" t="inlineStr">
+      <c r="X72" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y71" s="2" t="inlineStr">
+      <c r="Y72" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z71" s="2" t="inlineStr">
+      <c r="Z72" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA71" s="2" t="inlineStr">
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>79.4</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB71" s="2" t="inlineStr">
-        <is>
-          <t>80.2</t>
-        </is>
-      </c>
-      <c r="AC71" s="2" t="inlineStr">
-        <is>
-          <t>13/15</t>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>76.8</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>77.5</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>77.2</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-03-浦东78路.xlsx
+++ b/data/export/2026-10-03-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC78"/>
+  <dimension ref="A1:AC87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,17 +823,17 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,22 +1418,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1537,22 +1537,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2005,17 +2005,17 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2239,22 +2239,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2477,22 +2477,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2715,22 +2715,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3072,22 +3072,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3191,22 +3191,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3429,17 +3429,17 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3667,22 +3667,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -3747,7 +3747,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -4039,7 +4039,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4262,22 +4262,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4619,22 +4619,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4738,22 +4738,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5091,17 +5091,17 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5210,22 +5210,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5329,22 +5329,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5458,12 +5458,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5686,22 +5686,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5805,17 +5805,17 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5924,17 +5924,17 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6043,17 +6043,17 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6162,22 +6162,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6281,22 +6281,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -6361,7 +6361,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6638,17 +6638,17 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6876,22 +6876,22 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6995,17 +6995,17 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7114,17 +7114,17 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7233,22 +7233,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA57" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -7313,7 +7313,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7352,22 +7352,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -7432,7 +7432,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7471,22 +7471,22 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7962,7 +7962,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -8000,24 +8000,24 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -8027,7 +8027,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -8109,32 +8109,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -8142,7 +8146,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8166,37 +8170,37 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA65" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -8224,32 +8228,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>11:50</t>
@@ -8257,7 +8265,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8281,32 +8289,32 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA66" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8372,7 +8380,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8411,7 +8419,7 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
@@ -8426,7 +8434,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -8454,32 +8462,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -8487,7 +8499,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8511,32 +8523,32 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8569,32 +8581,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -8602,7 +8618,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8626,37 +8642,37 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA69" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -8684,32 +8700,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -8717,7 +8737,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8741,37 +8761,37 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA70" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -8799,32 +8819,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -8832,7 +8856,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8856,32 +8880,32 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA71" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -8914,32 +8938,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
@@ -8947,7 +8975,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8971,37 +8999,37 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA72" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -9062,7 +9090,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9144,32 +9172,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -9177,7 +9209,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9201,37 +9233,37 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -9292,7 +9324,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9346,7 +9378,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -9407,7 +9439,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9456,12 +9488,12 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -9522,7 +9554,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9584,22 +9616,22 @@
       <c r="A78" s="2" t="inlineStr"/>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -9632,12 +9664,12 @@
       <c r="M78" s="2" t="inlineStr"/>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9651,47 +9683,1082 @@
       <c r="T78" s="2" t="inlineStr"/>
       <c r="U78" s="2" t="inlineStr">
         <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>75.3</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="V78" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W78" s="2" t="inlineStr">
+      <c r="W79" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X78" s="2" t="inlineStr">
+      <c r="X79" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y78" s="2" t="inlineStr">
+      <c r="Y79" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z78" s="2" t="inlineStr">
+      <c r="Z79" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA78" s="2" t="inlineStr">
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>79.7</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB78" s="2" t="inlineStr">
+      <c r="AB80" s="2" t="inlineStr">
         <is>
           <t>77.2</t>
         </is>
       </c>
-      <c r="AC78" s="2" t="inlineStr">
+      <c r="AC80" s="2" t="inlineStr">
         <is>
           <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>79.8</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>14/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>77.6</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>75.2</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>74.6</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>14/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>76.4</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-03-浦东78路.xlsx
+++ b/data/export/2026-10-03-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC87"/>
+  <dimension ref="A1:AC94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1299,17 +1299,17 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1656,22 +1656,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,22 +1775,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2839,17 +2839,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3077,12 +3077,12 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3310,22 +3310,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3548,22 +3548,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3677,12 +3677,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3747,7 +3747,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4143,17 +4143,17 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4505,17 +4505,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4853,22 +4853,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5339,12 +5339,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5453,17 +5453,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6172,12 +6172,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6291,12 +6291,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -6361,7 +6361,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6480,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6519,22 +6519,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -6599,7 +6599,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6643,12 +6643,12 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6757,22 +6757,22 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6881,12 +6881,12 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6956,7 +6956,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -7194,7 +7194,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7233,7 +7233,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7313,7 +7313,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7362,12 +7362,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -7432,7 +7432,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7590,22 +7590,22 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -7670,7 +7670,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7709,17 +7709,17 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7828,22 +7828,22 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -7908,7 +7908,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7947,7 +7947,7 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -8027,7 +8027,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8071,17 +8071,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8190,12 +8190,12 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8265,7 +8265,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8309,12 +8309,12 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8380,7 +8380,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8419,7 +8419,7 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
@@ -8499,7 +8499,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8553,7 +8553,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -8618,7 +8618,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8657,7 +8657,7 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
@@ -8672,7 +8672,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -8737,7 +8737,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8776,7 +8776,7 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
@@ -8856,7 +8856,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8948,24 +8948,24 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9024,12 +9024,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -9057,32 +9057,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -9090,7 +9094,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9114,32 +9118,32 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA73" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9182,24 +9186,24 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -9209,7 +9213,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9258,12 +9262,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -9324,7 +9328,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9363,7 +9367,7 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
@@ -9406,32 +9410,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -9439,7 +9447,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9463,17 +9471,17 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
@@ -9483,17 +9491,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -9521,32 +9529,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -9554,7 +9566,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9578,37 +9590,37 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA77" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -9636,32 +9648,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>11:50</t>
@@ -9669,7 +9685,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9693,17 +9709,17 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -9713,12 +9729,12 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9784,7 +9800,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9823,7 +9839,7 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -9866,32 +9882,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -9899,7 +9919,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9923,37 +9943,37 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -10014,7 +10034,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10068,7 +10088,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -10096,32 +10116,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -10129,7 +10153,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10153,17 +10177,17 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
@@ -10173,12 +10197,12 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
@@ -10244,7 +10268,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10283,7 +10307,7 @@
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA83" s="2" t="inlineStr">
@@ -10298,7 +10322,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -10359,7 +10383,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10398,7 +10422,7 @@
       </c>
       <c r="Z84" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA84" s="2" t="inlineStr">
@@ -10474,7 +10498,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10589,7 +10613,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10638,12 +10662,12 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -10651,22 +10675,22 @@
       <c r="A87" s="2" t="inlineStr"/>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -10699,12 +10723,12 @@
       <c r="M87" s="2" t="inlineStr"/>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10743,22 +10767,827 @@
       </c>
       <c r="Z87" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>78.6</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA87" s="2" t="inlineStr">
+      <c r="AA88" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AB87" s="2" t="inlineStr">
-        <is>
-          <t>76.4</t>
-        </is>
-      </c>
-      <c r="AC87" s="2" t="inlineStr">
-        <is>
-          <t>5/15</t>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>77.6</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>79.7</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>77.6</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>77.6</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>77.6</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>75.2</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-03-浦东78路.xlsx
+++ b/data/export/2026-10-03-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC94"/>
+  <dimension ref="A1:AC98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1066,12 +1066,12 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1304,12 +1304,12 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1661,17 +1661,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2363,12 +2363,12 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2720,17 +2720,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2834,14 +2834,14 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
           <t>77.4</t>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3315,17 +3315,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4148,12 +4148,12 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4267,17 +4267,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4500,14 +4500,14 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
           <t>77.4</t>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5215,17 +5215,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5448,14 +5448,14 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
           <t>77.4</t>
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5805,14 +5805,14 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
           <t>75.2</t>
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6286,12 +6286,12 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6480,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6524,17 +6524,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -6599,7 +6599,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6638,14 +6638,14 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
           <t>75.2</t>
@@ -6653,7 +6653,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -6718,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7000,12 +7000,12 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7238,17 +7238,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -7313,7 +7313,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7357,12 +7357,12 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7476,7 +7476,7 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7595,17 +7595,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -7670,7 +7670,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7714,12 +7714,12 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7843,7 +7843,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -7908,7 +7908,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8027,7 +8027,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8066,14 +8066,14 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA64" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
           <t>77.4</t>
@@ -8081,7 +8081,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8200,7 +8200,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -8265,7 +8265,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8304,14 +8304,14 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA66" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
           <t>75.2</t>
@@ -8319,7 +8319,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -8380,7 +8380,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8618,7 +8618,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8672,7 +8672,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -8737,7 +8737,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8781,17 +8781,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -8856,7 +8856,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8900,12 +8900,12 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9019,7 +9019,7 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
@@ -9029,7 +9029,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -9094,7 +9094,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9138,12 +9138,12 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9213,7 +9213,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9486,14 +9486,14 @@
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA76" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
           <t>77.4</t>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -9566,7 +9566,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9610,17 +9610,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -9685,7 +9685,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9724,14 +9724,14 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA78" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
           <t>75.2</t>
@@ -9739,7 +9739,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -9800,7 +9800,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9919,7 +9919,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9973,7 +9973,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -10153,7 +10153,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10207,7 +10207,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -10268,7 +10268,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10322,7 +10322,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -10350,32 +10350,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -10383,7 +10387,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10407,17 +10411,17 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
@@ -10427,17 +10431,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -10465,32 +10469,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -10498,7 +10506,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10522,17 +10530,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10542,12 +10550,12 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
@@ -10580,32 +10588,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
@@ -10613,7 +10625,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10637,17 +10649,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10657,7 +10669,7 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
@@ -10667,7 +10679,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -10695,32 +10707,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -10728,7 +10744,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10752,17 +10768,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10772,12 +10788,12 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
@@ -10810,32 +10826,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -10843,7 +10863,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10867,17 +10887,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10887,12 +10907,12 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
@@ -10958,7 +10978,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11073,7 +11093,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11188,7 +11208,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11242,7 +11262,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -11270,32 +11290,36 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -11303,7 +11327,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11327,17 +11351,17 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11347,17 +11371,17 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -11365,22 +11389,22 @@
       <c r="A93" s="2" t="inlineStr"/>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t>20:10</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -11413,12 +11437,12 @@
       <c r="M93" s="2" t="inlineStr"/>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11432,7 +11456,7 @@
       <c r="T93" s="2" t="inlineStr"/>
       <c r="U93" s="2" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="V93" s="2" t="inlineStr">
@@ -11467,12 +11491,12 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -11480,22 +11504,22 @@
       <c r="A94" s="2" t="inlineStr"/>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>20:40</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -11528,12 +11552,12 @@
       <c r="M94" s="2" t="inlineStr"/>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11547,45 +11571,505 @@
       <c r="T94" s="2" t="inlineStr"/>
       <c r="U94" s="2" t="inlineStr">
         <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>75.2</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>77.6</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
           <t>20:40</t>
         </is>
       </c>
-      <c r="V94" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W94" s="2" t="inlineStr">
+      <c r="W96" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X94" s="2" t="inlineStr">
+      <c r="X96" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y94" s="2" t="inlineStr">
+      <c r="Y96" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z94" s="2" t="inlineStr">
+      <c r="Z96" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA94" s="2" t="inlineStr">
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>75.7</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AB94" s="2" t="inlineStr">
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>77.4</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
         <is>
           <t>75.2</t>
         </is>
       </c>
-      <c r="AC94" s="2" t="inlineStr">
+      <c r="AC98" s="2" t="inlineStr">
         <is>
           <t>2/15</t>
         </is>

--- a/data/export/2026-10-03-浦东78路.xlsx
+++ b/data/export/2026-10-03-浦东78路.xlsx
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1666,12 +1666,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2839,17 +2839,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3553,17 +3553,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3682,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4267,12 +4267,12 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4386,17 +4386,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4505,17 +4505,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4858,17 +4858,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5215,12 +5215,12 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5453,17 +5453,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5572,17 +5572,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6361,7 +6361,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6405,17 +6405,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -6599,7 +6599,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6643,12 +6643,12 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6762,17 +6762,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -7194,7 +7194,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7238,12 +7238,12 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7367,7 +7367,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7833,17 +7833,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -7908,7 +7908,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7952,17 +7952,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -8027,7 +8027,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8071,17 +8071,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -8265,7 +8265,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8309,12 +8309,12 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8672,7 +8672,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -8737,7 +8737,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9372,17 +9372,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -9447,7 +9447,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9491,17 +9491,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -9566,7 +9566,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9615,12 +9615,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -9685,7 +9685,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9729,12 +9729,12 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9919,7 +9919,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9963,17 +9963,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -10322,7 +10322,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -10387,7 +10387,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10431,12 +10431,12 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
@@ -10917,7 +10917,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -10945,32 +10945,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -10978,7 +10982,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11002,17 +11006,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -11022,17 +11026,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -11262,7 +11266,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -11300,24 +11304,24 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>20:53</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -11327,7 +11331,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11376,12 +11380,12 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -11409,32 +11413,36 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -11442,7 +11450,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11466,17 +11474,17 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -11486,17 +11494,17 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -11524,32 +11532,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>11:50</t>
@@ -11557,7 +11569,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11581,17 +11593,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11601,12 +11613,12 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
@@ -11639,32 +11651,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -11672,7 +11688,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11696,17 +11712,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11716,17 +11732,17 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -11754,32 +11770,36 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:53</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -11787,7 +11807,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11811,17 +11831,17 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -11831,12 +11851,12 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
@@ -11902,7 +11922,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11946,17 +11966,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -12017,7 +12037,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12061,12 +12081,12 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">

--- a/data/export/2026-10-03-浦东78路.xlsx
+++ b/data/export/2026-10-03-浦东78路.xlsx
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2839,17 +2839,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3682,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4505,17 +4505,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5220,7 +5220,7 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5453,17 +5453,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -6599,7 +6599,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7243,7 +7243,7 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7367,7 +7367,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -8027,7 +8027,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8071,17 +8071,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -8265,7 +8265,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8737,7 +8737,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -9447,7 +9447,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9491,17 +9491,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -9685,7 +9685,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -10387,7 +10387,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10436,7 +10436,7 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
@@ -10917,7 +10917,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -11450,7 +11450,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11494,17 +11494,17 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -11569,7 +11569,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11780,24 +11780,24 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>21:53</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -11807,7 +11807,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
@@ -11889,32 +11889,36 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:23</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -11922,7 +11926,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11946,17 +11950,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -11966,17 +11970,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -12037,7 +12041,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
